--- a/data.xlsx
+++ b/data.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{AAB1F1DD-F28C-4093-B97B-301FAD7B691C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4383CD73-C60B-4D89-A99B-C7FA5FC03F75}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{AAB1F1DD-F28C-4093-B97B-301FAD7B691C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9042CF31-656C-4EC1-9815-4B4C8062C39B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -651,12 +664,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1053,8 +1069,8 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>4000200000000</v>
+      <c r="A2" s="2">
+        <v>4000196031150</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -1064,8 +1080,8 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
-        <v>8801230000000</v>
+      <c r="A3" s="2">
+        <v>8801230160609</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
@@ -1075,7 +1091,7 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+      <c r="A4" s="2">
         <v>9702040100</v>
       </c>
       <c r="B4" t="s">

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAEEUNG\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{AAB1F1DD-F28C-4093-B97B-301FAD7B691C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9042CF31-656C-4EC1-9815-4B4C8062C39B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -54,12 +54,6 @@
   </si>
   <si>
     <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDyPnOd3EVqT68K7o7gvGNqARrYcpvjmsACEIuzp0Pkucc?e=0IBKW0</t>
-  </si>
-  <si>
-    <t>PCD 용접 외관 기준</t>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAXkKmG-_hjRLUa22MKGBDAAamtdb-bmfELqF9Orm9Lmpg?e=SB1A니</t>
   </si>
   <si>
     <t>20240119409100X</t>
@@ -664,15 +658,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1049,7 +1040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1069,7 +1060,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>4000196031150</v>
       </c>
       <c r="B2" t="s">
@@ -1080,7 +1071,7 @@
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>8801230160609</v>
       </c>
       <c r="B3" t="s">
@@ -1091,25 +1082,14 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>9702040100</v>
+      <c r="A4" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" t="s">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DAEEUNG\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C149C9F3-3EEF-49C6-A539-D76A5B2B8821}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -47,13 +47,7 @@
     <t>HILTI빗각외경드레싱</t>
   </si>
   <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAf2d-0inNzSLBpZ6iuHzu9AVbFeZj96w8VHnVJ5EXimGM?e=UeZp2K</t>
-  </si>
-  <si>
     <t>실크스크린</t>
-  </si>
-  <si>
-    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDyPnOd3EVqT68K7o7gvGNqARrYcpvjmsACEIuzp0Pkucc?e=0IBKW0</t>
   </si>
   <si>
     <t>20240119409100X</t>
@@ -62,7 +56,23 @@
     <t>이화 별색 페인트</t>
   </si>
   <si>
+    <t>PCD 용접 외관 기준</t>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAXkKmG-_hjRLUa22MKGBDAAamtdb-bmfELqF9Orm9Lmpg?e=NVECRj</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
     <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDamsLEktjJSrYkJqHmsLB4Ab-WIrLkJofa4Dh-19l0axM?e=Zeu04D</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDyPnOd3EVqT68K7o7gvGNqARrYcpvjmsACEIuzp0Pkucc?e=0IBKW0</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAf2d-0inNzSLBpZ6iuHzu9AVbFeZj96w8VHnVJ5EXimGM?e=UeZp2K</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -72,7 +82,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +237,15 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -530,7 +549,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -657,16 +676,22 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 강조색1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 강조색2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 강조색3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -709,6 +734,7 @@
     <cellStyle name="좋음" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="출력" xfId="10" builtinId="21" customBuiltin="1"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="42" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1040,7 +1066,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1066,8 +1092,8 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -1075,26 +1101,43 @@
         <v>8801230160609</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>6</v>
+        <v>4</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>9702040100</v>
+      </c>
+      <c r="B5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C5" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" xr:uid="{02CACEB8-149A-40E6-97F1-171D6C7C02C7}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{76EDF735-7D54-4D5E-A122-602E991AB92D}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{D48176E5-F1A0-43FA-BBE6-CAB7C1A3E4D4}"/>
+    <hyperlink ref="C2" r:id="rId4" xr:uid="{E221CE52-5D4B-47BE-8BB9-1B70CD524B11}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C149C9F3-3EEF-49C6-A539-D76A5B2B8821}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADC00B58-0DB0-4B9E-B688-811CC2FED24E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>실크스크린</t>
-  </si>
-  <si>
-    <t>20240119409100X</t>
   </si>
   <si>
     <t>이화 별색 페인트</t>
@@ -72,6 +69,22 @@
   </si>
   <si>
     <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAf2d-0inNzSLBpZ6iuHzu9AVbFeZj96w8VHnVJ5EXimGM?e=UeZp2K</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>20240119409100X</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>P100035</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDjRwHRmzQXRaNbWwiQM3IQAReLvKoQzNdxBBxKqCDeUiM?e=7vF83m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>클리어런스 측정법</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -680,7 +693,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -689,6 +702,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1066,7 +1082,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1086,47 +1102,58 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2" s="3">
         <v>4000196031150</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3" s="3">
         <v>8801230160609</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+      <c r="A5" s="3">
         <v>9702040100</v>
       </c>
       <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1136,8 +1163,9 @@
     <hyperlink ref="C4" r:id="rId2" xr:uid="{76EDF735-7D54-4D5E-A122-602E991AB92D}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{D48176E5-F1A0-43FA-BBE6-CAB7C1A3E4D4}"/>
     <hyperlink ref="C2" r:id="rId4" xr:uid="{E221CE52-5D4B-47BE-8BB9-1B70CD524B11}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{90160BE3-10BD-4487-B3DF-7421389189F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADC00B58-0DB0-4B9E-B688-811CC2FED24E}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83EF5FF0-32CB-4F76-96D1-4AD584AC0465}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -85,6 +85,18 @@
   </si>
   <si>
     <t>클리어런스 측정법</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQCbJBfYrTWWS73HC4n8QLlqAVlx0Mzy_BkTlZly81o5jWo?e=l85bkH</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>2608F02506</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>BOSCH DIABLO TU-3"</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1082,7 +1094,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1156,6 +1168,17 @@
         <v>13</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
@@ -1164,8 +1187,9 @@
     <hyperlink ref="C3" r:id="rId3" xr:uid="{D48176E5-F1A0-43FA-BBE6-CAB7C1A3E4D4}"/>
     <hyperlink ref="C2" r:id="rId4" xr:uid="{E221CE52-5D4B-47BE-8BB9-1B70CD524B11}"/>
     <hyperlink ref="C6" r:id="rId5" xr:uid="{90160BE3-10BD-4487-B3DF-7421389189F9}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{E7D2CBF0-4C01-4C44-9E2D-6FA897398692}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83EF5FF0-32CB-4F76-96D1-4AD584AC0465}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A95631-9E20-4813-9BE9-AC2D4759F544}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -89,10 +89,6 @@
   </si>
   <si>
     <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQCbJBfYrTWWS73HC4n8QLlqAVlx0Mzy_BkTlZly81o5jWo?e=l85bkH</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
-    <t>2608F02506</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
@@ -705,7 +701,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -716,6 +712,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1169,11 +1168,11 @@
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="4">
+        <v>26083025061</v>
+      </c>
+      <c r="B7" t="s">
         <v>16</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>15</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E8A95631-9E20-4813-9BE9-AC2D4759F544}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C212DDFF-E689-440A-8B88-4C8C0B08A4B2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -1093,7 +1093,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1161,10 +1161,10 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1172,11 +1172,14 @@
         <v>26083025061</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>15</v>
-      </c>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C8" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -1185,8 +1188,8 @@
     <hyperlink ref="C4" r:id="rId2" xr:uid="{76EDF735-7D54-4D5E-A122-602E991AB92D}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{D48176E5-F1A0-43FA-BBE6-CAB7C1A3E4D4}"/>
     <hyperlink ref="C2" r:id="rId4" xr:uid="{E221CE52-5D4B-47BE-8BB9-1B70CD524B11}"/>
-    <hyperlink ref="C6" r:id="rId5" xr:uid="{90160BE3-10BD-4487-B3DF-7421389189F9}"/>
-    <hyperlink ref="C7" r:id="rId6" xr:uid="{E7D2CBF0-4C01-4C44-9E2D-6FA897398692}"/>
+    <hyperlink ref="C6" r:id="rId5" xr:uid="{DEAA650C-81B6-4189-9899-65C790140C23}"/>
+    <hyperlink ref="C7" r:id="rId6" xr:uid="{9D742E63-421D-4B15-ABA5-71740F93A294}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C212DDFF-E689-440A-8B88-4C8C0B08A4B2}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A598C6D-2001-42A6-B717-EA2AAB28B4FD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -93,6 +93,14 @@
   </si>
   <si>
     <t>BOSCH DIABLO TU-3"</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>HILTI BS-14</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAIYCuHYaLORL3onZApx-wBAdrndDC57oMo2cJSdIrP2ks?e=de4bt6</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1094,14 +1102,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="105.375" customWidth="1"/>
+    <col min="2" max="2" width="19.69921875" customWidth="1"/>
+    <col min="3" max="3" width="105.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1120,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="3">
         <v>4000196031150</v>
       </c>
@@ -1123,7 +1131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="3">
         <v>8801230160609</v>
       </c>
@@ -1134,7 +1142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
@@ -1145,7 +1153,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="3">
         <v>9702040100</v>
       </c>
@@ -1156,7 +1164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>12</v>
       </c>
@@ -1167,7 +1175,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="4">
         <v>26083025061</v>
       </c>
@@ -1178,8 +1186,16 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C8" s="2"/>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="1">
+        <v>2434817</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
@@ -1190,8 +1206,9 @@
     <hyperlink ref="C2" r:id="rId4" xr:uid="{E221CE52-5D4B-47BE-8BB9-1B70CD524B11}"/>
     <hyperlink ref="C6" r:id="rId5" xr:uid="{DEAA650C-81B6-4189-9899-65C790140C23}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{9D742E63-421D-4B15-ABA5-71740F93A294}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{EA7565F5-47D8-44A0-A014-697F13F23F50}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A598C6D-2001-42A6-B717-EA2AAB28B4FD}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1C269A-497A-40F4-8FAB-8E1A3B4B9D3D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -102,6 +102,93 @@
   <si>
     <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAIYCuHYaLORL3onZApx-wBAdrndDC57oMo2cJSdIrP2ks?e=de4bt6</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>V28004020_Cutting disc 100/20/16mm SPX metal</t>
+  </si>
+  <si>
+    <t>V28405057_Cutting disc 115/22mm SPX metal</t>
+  </si>
+  <si>
+    <t>V28005030_Cutting disc 125/22mm SPX metal</t>
+  </si>
+  <si>
+    <t>V28009012_Cutting disc 230/22mm SPX metal</t>
+  </si>
+  <si>
+    <t>V28012052_Cutting disc 300/25mm SPX metal</t>
+  </si>
+  <si>
+    <t>V28014025_Cutting disc 350/25mm SPX metal</t>
+  </si>
+  <si>
+    <t>V28016037_Cutting disc 400/25mm SPX metal</t>
+  </si>
+  <si>
+    <t>V28405057_Dia blade 115/22 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28005030_Dia blade 125/22 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28009012_Dia blade 230/22 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28012104_Dia blade 300/25 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28014173_Dia blade 350/25 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28016077_Dia blade 400/25 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28005110_Dia blade 125/22 SPX chamfer</t>
+  </si>
+  <si>
+    <t>V28009105_Dia blade 230/22 SPX chamfer</t>
+  </si>
+  <si>
+    <t>V28012107_Dia blade 300/25 SPX chamfer</t>
+  </si>
+  <si>
+    <t>V28012105_Dia blade 300/20 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28014174_Dia blade 350/20 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28016078_Dia blade 400/20 SPX metal/PVC</t>
+  </si>
+  <si>
+    <t>V28012106_Dia blade 300/20 SPX chamfer</t>
+  </si>
+  <si>
+    <t>V10012215_Dia blade 300/25 SPX granite</t>
+  </si>
+  <si>
+    <t>V10014366_Dia blade 350/25 SPX granite</t>
+  </si>
+  <si>
+    <t>V10016167_Dia blade 400/25 SPX granite</t>
+  </si>
+  <si>
+    <t>V10012214_Dia blade 300/20 SPX granite</t>
+  </si>
+  <si>
+    <t>V10014365_Dia blade 350/20 SPX granite</t>
+  </si>
+  <si>
+    <t>V10016166_Dia blade 400/20 SPX granite</t>
+  </si>
+  <si>
+    <t>V50105029_Diamond wire DS-W 10.5-100m SI SP-M/H</t>
+  </si>
+  <si>
+    <t>V50105030_Diamond wire DS-W 10.5-50m SI SP-M/H</t>
+  </si>
+  <si>
+    <t>V50105037_Diamond wire DS-W 10.5-25m SI SP-M/H</t>
   </si>
 </sst>
 </file>
@@ -709,7 +796,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -724,6 +811,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1101,7 +1194,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1195,6 +1288,238 @@
       </c>
       <c r="C8" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="5">
+        <v>2314163</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="5">
+        <v>2314164</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="5">
+        <v>2314165</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="5">
+        <v>2314166</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="5">
+        <v>2314167</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="5">
+        <v>2314168</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="5">
+        <v>2314169</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="5">
+        <v>2384228</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A17" s="5">
+        <v>2384229</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A18" s="5">
+        <v>2384232</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A19" s="5">
+        <v>2384233</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A20" s="5">
+        <v>2384234</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A21" s="5">
+        <v>2384235</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A22" s="5">
+        <v>2384236</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A23" s="5">
+        <v>2384237</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A24" s="5">
+        <v>2384238</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A25" s="5">
+        <v>2390326</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A26" s="5">
+        <v>2390327</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A27" s="5">
+        <v>2390328</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A28" s="5">
+        <v>2390329</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A29" s="5">
+        <v>2384224</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A30" s="5">
+        <v>2384225</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A31" s="5">
+        <v>2384226</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A32" s="5">
+        <v>2390320</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A33" s="5">
+        <v>2390321</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A34" s="5">
+        <v>2390322</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A35" s="5">
+        <v>2299889</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A36" s="5">
+        <v>2299890</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A37" s="5">
+        <v>2299891</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/02.공정개선/2026/QAI_K_260622_Claude_바코드 포장지도서 검색 프로그램/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ehwadia-my.sharepoint.com/personal/icdide_ehwadia_onmicrosoft_com/Documents/서버_품질보증/00.고객심사/2026년09월08일_베트남_HILTI_Sagar,Rex/포장지도서/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B1C269A-497A-40F4-8FAB-8E1A3B4B9D3D}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{3AB410EC-287A-47C1-A970-3EAE29AF03EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C41D2699-AC96-4610-A53E-7C5346630DCA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C7102F99-5A4F-4714-A560-4A1A2B659E8E}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>바코드스캔</t>
   </si>
@@ -189,6 +189,37 @@
   </si>
   <si>
     <t>V50105037_Diamond wire DS-W 10.5-25m SI SP-M/H</t>
+  </si>
+  <si>
+    <t>P118855HILTI(LI)BS-14(2)_2384234.pdf</t>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQB8fW-ZPPtXQIRteVPgSh3iAUG67d1mrWxlvaeh4HXxnu4?e=8IqRRb</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDQMk7VJZc4Tpr3L1cxPSfyAQIrH1NIEGy8wjmOjnzSWiE?e=EyDctk</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DS-W 10.5 VB CL 27.75</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>DS-W 10.5 VB-SPX-H C&amp;S</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQBYeb7Z9whsTJPfUmsnjFt0AQlrU9M_IKktEipgRtay0fg?e=j27RHj</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQArz5Fb_foGRL2fCjFEAMHzAS-BdQ8OsjPa75qkL8_oCRA?e=BhhHGe</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://ehwadia-my.sharepoint.com/:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQDE0JsK9kIqT6vANYh_Kw7mAUOOPi1X4KrzMAjpsK4H2hQ?e=oFcVjQ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -796,7 +827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -811,12 +842,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1194,7 +1219,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A1E5B56-C730-4A56-A787-73EB347061DA}">
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C40"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="28.5" style="1" customWidth="1"/>
@@ -1291,235 +1316,274 @@
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>2314163</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>2314164</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>2314165</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>2314166</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" t="s">
         <v>22</v>
       </c>
+      <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>2314167</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>2314168</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>2314169</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>2384228</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" s="5">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="4">
         <v>2384229</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" s="5">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="4">
         <v>2384232</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" s="5">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="4">
         <v>2384233</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" s="5">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="4">
         <v>2384234</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A21" s="5">
+      <c r="C20" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="4">
         <v>2384235</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A22" s="5">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="4">
         <v>2384236</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A23" s="5">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="4">
         <v>2384237</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A24" s="5">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="4">
         <v>2384238</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A25" s="5">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="4">
         <v>2390326</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A26" s="5">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="4">
         <v>2390327</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A27" s="5">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="4">
         <v>2390328</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A28" s="5">
+      <c r="C27" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="4">
         <v>2390329</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A29" s="5">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A29" s="4">
         <v>2384224</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A30" s="5">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A30" s="4">
         <v>2384225</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A31" s="5">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A31" s="4">
         <v>2384226</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A32" s="5">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A32" s="4">
         <v>2390320</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A33" s="5">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="4">
         <v>2390321</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A34" s="5">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="4">
         <v>2390322</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" s="5">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="4">
         <v>2299889</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A36" s="5">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="4">
         <v>2299890</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" s="5">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="4">
         <v>2299891</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="1">
+        <v>2453626</v>
+      </c>
+      <c r="B38" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="1">
+        <v>2453625</v>
+      </c>
+      <c r="B39" t="s">
+        <v>51</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="1">
+        <v>2254450</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1532,8 +1596,14 @@
     <hyperlink ref="C6" r:id="rId5" xr:uid="{DEAA650C-81B6-4189-9899-65C790140C23}"/>
     <hyperlink ref="C7" r:id="rId6" xr:uid="{9D742E63-421D-4B15-ABA5-71740F93A294}"/>
     <hyperlink ref="C8" r:id="rId7" xr:uid="{EA7565F5-47D8-44A0-A014-697F13F23F50}"/>
+    <hyperlink ref="C20" r:id="rId8" display="../../../../../../../:b:/g/personal/icdide_ehwadia_onmicrosoft_com/IQAv2rp4HVTlT6AXXf-COyjcAekvmjjC3cGEGeaGIr1Vw6g?e=m7cmwH" xr:uid="{C9B83105-B6A6-416A-81FD-9941FE1FBD77}"/>
+    <hyperlink ref="C38" r:id="rId9" xr:uid="{1E52F091-1AB2-4194-A718-08968B95F4B3}"/>
+    <hyperlink ref="C39" r:id="rId10" xr:uid="{1A373658-EA00-46F5-A334-939B1092C9A3}"/>
+    <hyperlink ref="C27" r:id="rId11" xr:uid="{03635319-FBCC-46EC-840B-8E887FA6C662}"/>
+    <hyperlink ref="C12" r:id="rId12" xr:uid="{89FA1357-6F15-4D8E-AC48-C42955AC5363}"/>
+    <hyperlink ref="C40" r:id="rId13" xr:uid="{0BF5B71A-BE82-463E-88C2-CC8C1C665DC8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId8"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId14"/>
 </worksheet>
 </file>